--- a/Exceptions_ComparissonDB.xlsx
+++ b/Exceptions_ComparissonDB.xlsx
@@ -5,22 +5,35 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\w10itasv\Documents\Andres Work\ComparisonTableTool\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\w10itasv\Documents\DevDataMigration\DevDataMigrationTool\GitHubDataMigration\DataMigrationTool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69DA00CA-D5BB-456E-A737-30F5FE692DDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3D18679-924D-4A66-BC12-35A2320F524C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32370" yWindow="1905" windowWidth="10080" windowHeight="8370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Exceptions" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="27">
   <si>
     <t>COLUMN_NAME</t>
   </si>
@@ -89,13 +102,25 @@
   </si>
   <si>
     <t>CUIC</t>
+  </si>
+  <si>
+    <t>DTL2</t>
+  </si>
+  <si>
+    <t>BPCD</t>
+  </si>
+  <si>
+    <t>PYOP</t>
+  </si>
+  <si>
+    <t>CUST</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -109,6 +134,12 @@
     <font>
       <sz val="8"/>
       <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF161618"/>
+      <name val="Source Sans Pro"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -136,12 +167,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -160,7 +192,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ExceptionsTable" displayName="ExceptionsTable" ref="A1:C20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ExceptionsTable" displayName="ExceptionsTable" ref="A1:C24">
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="COLUMN_NAME"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="ACTIVE"/>
@@ -319,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -555,6 +587,50 @@
         <v>10</v>
       </c>
     </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" t="s">
+        <v>3</v>
+      </c>
+      <c r="C21" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="15">
+      <c r="A22" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B22" t="s">
+        <v>3</v>
+      </c>
+      <c r="C22" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23" t="s">
+        <v>3</v>
+      </c>
+      <c r="C23" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" t="s">
+        <v>3</v>
+      </c>
+      <c r="C24" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
